--- a/data/data_minerals/WMD/6.2. World_Production_of_Mineral_Raw_Materials_by_ Mineral_Raw_Materials.xlsx
+++ b/data/data_minerals/WMD/6.2. World_Production_of_Mineral_Raw_Materials_by_ Mineral_Raw_Materials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals/New_version_marin/data_minerals/WMD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals_github/plca_metals/data/data_minerals/WMD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_0725704D6D0B81DFD69091C1D4BFBBE1C2C3C3D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82CB88A3-9287-4C79-A49A-F1862326344C}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_0725704D6D0B81DFD69091C1D4BFBBE1C2C3C3D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{014C5D8A-35C9-40B4-8DB8-7B2AFD5BDF0C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="678" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -892,7 +892,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="49" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
@@ -921,6 +921,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="11" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="26" fillId="33" borderId="11" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="20% - Accent1" xfId="24" builtinId="30" hidden="1"/>
@@ -1573,6 +1579,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="6.2.1.Iron &amp; Ferro-Alloy Metals" displayName="_6.2.1.Iron___Ferro_Alloy_Metals" ref="A2:G13" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" headerRowCellStyle="Tabelle Kopf" dataCellStyle="Tabelle allgemein">
   <tableColumns count="7">
@@ -1941,7 +1951,8 @@
     <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
@@ -1954,19 +1965,19 @@
       <c r="C1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="12" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2226,7 +2237,7 @@
       <c r="G11" s="10">
         <v>4922770</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="13">
         <v>5346091</v>
       </c>
     </row>
